--- a/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,28; 92,69</t>
+          <t>72,83; 93,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,96; 94,72</t>
+          <t>76,67; 94,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,84; 92,24</t>
+          <t>78,29; 92,16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,09; 95,92</t>
+          <t>76,99; 96,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,77; 81,28</t>
+          <t>50,65; 81,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,08; 90,33</t>
+          <t>69,11; 89,63</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,7; 83,48</t>
+          <t>56,52; 81,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,0; 92,08</t>
+          <t>72,79; 92,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,49; 84,9</t>
+          <t>68,03; 84,97</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,66; 89,58</t>
+          <t>59,87; 88,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,03; 79,95</t>
+          <t>40,77; 80,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,93; 80,65</t>
+          <t>56,21; 82,09</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,66; 52,26</t>
+          <t>24,4; 50,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,3; 60,42</t>
+          <t>30,64; 59,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,45; 50,81</t>
+          <t>30,74; 50,88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,78; 95,22</t>
+          <t>70,72; 94,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,61; 87,91</t>
+          <t>66,24; 88,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,39; 89,04</t>
+          <t>71,74; 88,76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57,4; 79,33</t>
+          <t>59,74; 79,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,94; 70,86</t>
+          <t>49,42; 70,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,58; 72,43</t>
+          <t>56,63; 72,19</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>73,82; 90,14</t>
+          <t>73,27; 90,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,03; 97,02</t>
+          <t>87,56; 97,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,09; 92,91</t>
+          <t>83,6; 92,65</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>72,94; 83,11</t>
+          <t>72,62; 82,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,78; 78,79</t>
+          <t>69,59; 78,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,56; 79,51</t>
+          <t>72,88; 79,43</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>28963</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37084</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66047</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24907; 31932</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32389; 39926</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59850; 70451</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>68889</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42561</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>111450</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>60318; 75328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30890; 49742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96291; 124882</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>21024</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26276</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>16647; 24094</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22875; 29108</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41418; 51727</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22558</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16014</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38571</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>17651; 26097</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10653; 21105</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31258; 45651</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8639</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11966</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20604</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5821; 11955</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8372; 16347</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15737; 26044</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>17908</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26231</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>44139</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>14726; 19717</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22072; 29492</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>38843; 48060</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>39753</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>48614</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>88366</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>33725; 45045</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>39361; 55882</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>77073; 98247</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>48943</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>79549</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>128493</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>43171; 53235</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>74493; 82613</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>120377; 133408</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>256677</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>288294</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>544970</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>240776; 274374</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>268712; 303539</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>523082; 570088</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,83; 93,37</t>
+          <t>72,74; 93,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,67; 94,51</t>
+          <t>76,36; 95,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,29; 92,16</t>
+          <t>78,93; 92,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,99; 96,15</t>
+          <t>76,62; 96,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,65; 81,57</t>
+          <t>52,56; 81,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,11; 89,63</t>
+          <t>69,75; 89,39</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,52; 81,8</t>
+          <t>55,91; 83,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,79; 92,62</t>
+          <t>71,32; 92,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,03; 84,97</t>
+          <t>68,28; 85,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,87; 88,51</t>
+          <t>59,97; 89,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,77; 80,77</t>
+          <t>40,3; 80,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,21; 82,09</t>
+          <t>56,43; 80,79</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,4; 50,1</t>
+          <t>23,58; 51,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,64; 59,82</t>
+          <t>29,84; 59,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 50,88</t>
+          <t>31,09; 50,32</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,72; 94,69</t>
+          <t>69,82; 94,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,24; 88,51</t>
+          <t>64,63; 88,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,74; 88,76</t>
+          <t>72,49; 88,76</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,74; 79,79</t>
+          <t>59,01; 80,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,42; 70,17</t>
+          <t>50,42; 71,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,63; 72,19</t>
+          <t>56,82; 72,15</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>73,27; 90,35</t>
+          <t>72,06; 89,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,56; 97,11</t>
+          <t>88,34; 96,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,6; 92,65</t>
+          <t>84,21; 92,8</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>72,62; 82,76</t>
+          <t>73,19; 82,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,59; 78,61</t>
+          <t>69,54; 78,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,88; 79,43</t>
+          <t>72,34; 79,33</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24907; 31932</t>
+          <t>24878; 31840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32389; 39926</t>
+          <t>32260; 40233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59850; 70451</t>
+          <t>60342; 70940</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60318; 75328</t>
+          <t>60031; 75529</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30890; 49742</t>
+          <t>32053; 49836</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96291; 124882</t>
+          <t>97184; 124540</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16647; 24094</t>
+          <t>16468; 24643</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22875; 29108</t>
+          <t>22413; 29006</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41418; 51727</t>
+          <t>41570; 52187</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17651; 26097</t>
+          <t>17680; 26456</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10653; 21105</t>
+          <t>10530; 20980</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31258; 45651</t>
+          <t>31383; 44931</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5821; 11955</t>
+          <t>5627; 12169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8372; 16347</t>
+          <t>8154; 16175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15737; 26044</t>
+          <t>15913; 25756</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14726; 19717</t>
+          <t>14539; 19759</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22072; 29492</t>
+          <t>21536; 29588</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38843; 48060</t>
+          <t>39251; 48058</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33725; 45045</t>
+          <t>33312; 45266</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39361; 55882</t>
+          <t>40156; 56722</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77073; 98247</t>
+          <t>77336; 98195</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>43171; 53235</t>
+          <t>42459; 52996</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>74493; 82613</t>
+          <t>75157; 82492</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>120377; 133408</t>
+          <t>121259; 133626</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>240776; 274374</t>
+          <t>242664; 275054</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>268712; 303539</t>
+          <t>268513; 303444</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>523082; 570088</t>
+          <t>519201; 569331</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,74; 93,1</t>
+          <t>74,86; 94,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,36; 95,24</t>
+          <t>69,67; 91,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,93; 92,8</t>
+          <t>76,77; 91,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,62; 96,4</t>
+          <t>50,34; 82,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,56; 81,72</t>
+          <t>71,93; 89,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,75; 89,39</t>
+          <t>64,62; 83,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,08%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,91; 83,67</t>
+          <t>70,88; 91,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,32; 92,3</t>
+          <t>57,96; 84,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,28; 85,72</t>
+          <t>69,26; 85,28</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,97; 89,73</t>
+          <t>38,76; 80,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,3; 80,29</t>
+          <t>57,23; 89,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,43; 80,79</t>
+          <t>54,91; 80,67</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,58; 51,0</t>
+          <t>29,44; 59,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,84; 59,19</t>
+          <t>23,76; 50,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,09; 50,32</t>
+          <t>29,73; 49,99</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,82; 94,89</t>
+          <t>64,7; 88,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,63; 88,8</t>
+          <t>71,88; 95,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72,49; 88,76</t>
+          <t>73,02; 89,61</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,01; 80,18</t>
+          <t>50,79; 71,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50,42; 71,22</t>
+          <t>54,99; 77,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56,82; 72,15</t>
+          <t>57,04; 71,61</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>72,06; 89,95</t>
+          <t>87,01; 97,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,34; 96,97</t>
+          <t>73,16; 89,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,21; 92,8</t>
+          <t>83,81; 92,98</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73,19; 82,96</t>
+          <t>69,8; 78,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,54; 78,58</t>
+          <t>70,41; 78,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72,34; 79,33</t>
+          <t>71,34; 77,37</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24878; 31840</t>
+          <t>24721; 31102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32260; 40233</t>
+          <t>20226; 26622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60342; 70940</t>
+          <t>47638; 56701</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>80811</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60031; 75529</t>
+          <t>27443; 44823</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32053; 49836</t>
+          <t>37401; 46530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97184; 124540</t>
+          <t>68823; 88941</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>44323</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16468; 24643</t>
+          <t>19793; 25667</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22413; 29006</t>
+          <t>16717; 24303</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41570; 52187</t>
+          <t>39317; 48411</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38377</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17680; 26456</t>
+          <t>9763; 20172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10530; 20980</t>
+          <t>17261; 27013</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31383; 44931</t>
+          <t>30391; 44649</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20391</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5627; 12169</t>
+          <t>8107; 16294</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8154; 16175</t>
+          <t>5784; 12329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15913; 25756</t>
+          <t>15427; 25938</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>40829</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14539; 19759</t>
+          <t>18873; 25785</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21536; 29588</t>
+          <t>14846; 19655</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39251; 48058</t>
+          <t>36381; 44647</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88366</t>
+          <t>83116</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33312; 45266</t>
+          <t>37876; 53272</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40156; 56722</t>
+          <t>30296; 42599</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77336; 98195</t>
+          <t>73969; 92859</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>48943</t>
+          <t>80443</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>79549</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128493</t>
+          <t>130561</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>42459; 52996</t>
+          <t>74852; 83528</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>75157; 82492</t>
+          <t>44367; 54447</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>121259; 133626</t>
+          <t>122920; 136366</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>351</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>256677</t>
+          <t>266611</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>242664; 275054</t>
+          <t>249873; 282316</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>268513; 303444</t>
+          <t>211785; 236506</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>519201; 569331</t>
+          <t>469918; 509658</t>
         </is>
       </c>
     </row>
